--- a/output/pdf_financials_xlsx/VMS.xlsx
+++ b/output/pdf_financials_xlsx/VMS.xlsx
@@ -3781,16 +3781,16 @@
         <v>0</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.6018829999999999</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.671408</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.656248</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.047088</v>
       </c>
     </row>
     <row r="93">
@@ -6180,7 +6180,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -6721,7 +6725,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -7156,7 +7164,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -7898,7 +7910,11 @@
           <t>Reserves (Note 3 and 7)</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -11029,7 +11045,7 @@
         </is>
       </c>
       <c r="K94" s="5" t="n">
-        <v>1.896665</v>
+        <v>-1.896665</v>
       </c>
       <c r="L94" s="5" t="n">
         <v>-2.531609</v>

--- a/output/pdf_financials_xlsx/VMS.xlsx
+++ b/output/pdf_financials_xlsx/VMS.xlsx
@@ -822,10 +822,10 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.009766</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.050208</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -1370,10 +1370,10 @@
         <v>-0.187172</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-3.848557</v>
+        <v>-3.858323</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.896665</v>
+        <v>-1.946873</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-2.531609</v>
@@ -1438,10 +1438,10 @@
         <v>-0.187172</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-3.848557</v>
+        <v>-3.858323</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.896665</v>
+        <v>-1.946873</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-2.531609</v>
@@ -1607,28 +1607,28 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.655677</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.604199</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.524218</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.016732</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>2.070269</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.293871</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.159068</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.012837</v>
       </c>
     </row>
     <row r="35">
@@ -1679,28 +1679,28 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.655677</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.604199</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.524218</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.016732</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>2.070269</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.293871</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.159068</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.012837</v>
       </c>
     </row>
     <row r="37">
@@ -2111,28 +2111,28 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.658677</v>
+        <v>0.003</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.604199</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.524218</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>3.908002</v>
+        <v>3.89127</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.074972</v>
+        <v>0.004703</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.316769</v>
+        <v>0.022898</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.198796</v>
+        <v>0.039728</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.054083</v>
+        <v>0.041246</v>
       </c>
     </row>
     <row r="49">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -17862,7 +17862,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -18594,7 +18594,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">

--- a/output/pdf_financials_xlsx/VMS.xlsx
+++ b/output/pdf_financials_xlsx/VMS.xlsx
@@ -643,19 +643,19 @@
         <v>0.014931</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.009972</v>
+        <v>0.017217</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.189235</v>
+        <v>0.214159</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.206644</v>
+        <v>0.241688</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.187627</v>
+        <v>0.251433</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.144923</v>
+        <v>0.211015</v>
       </c>
     </row>
     <row r="8">
@@ -2846,13 +2846,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.04228</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.097639</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.173478</v>
       </c>
     </row>
     <row r="68">
@@ -4426,7 +4426,7 @@
         <v>0</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.008772</v>
       </c>
       <c r="J111" s="3" t="n">
         <v>0</v>
@@ -5242,7 +5242,7 @@
         <v>0</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.008772</v>
       </c>
       <c r="J134" s="3" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
         <v>-1.776398</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-1.918749</v>
+        <v>-1.927521</v>
       </c>
       <c r="J135" s="3" t="n">
         <v>-1.329607</v>
@@ -9795,7 +9795,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -9980,7 +9984,11 @@
           <t>Shares issued for cash, net (Note 7a)</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -11554,7 +11562,11 @@
           <t>Purchase of equipment (Note 4)</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -16666,7 +16678,11 @@
           <t>Office expense (Note 4)</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -18232,7 +18248,11 @@
           <t>Office expense (Note 5)</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -18960,7 +18980,11 @@
           <t>Office expense (Note 6)</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
